--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>8UHsapgU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2meCcXHP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>bJtrhBum</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>CrrhJmvn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ILdqjkAa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Qo0ilTvC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>n1l0n79O</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xQT96Aft</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>04EZ06OH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pCQRkLbJ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,29 +448,29 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1.95</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8UHsapgU</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -480,210 +480,1220 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2meCcXHP</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bJtrhBum</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>15.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CrrhJmvn</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ILdqjkAa</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Qo0ilTvC</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n1l0n79O</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xQT96Aft</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>04EZ06OH</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pCQRkLbJ</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>2.20</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4.75</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,242 +448,22 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>8UHsapgU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>2meCcXHP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>bJtrhBum</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>CrrhJmvn</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ILdqjkAa</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Qo0ilTvC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1l0n79O</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xQT96Aft</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>04EZ06OH</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pCQRkLbJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.20</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,49 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>odds_home</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds_draw</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>odds_away</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>AeRSxQrK</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,621 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,594 +448,1594 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vDEpovX1</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hxlYyYo4</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U32wGjPp</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hGzqjO6E</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OrHrRGXo</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WQF2UUMt</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rkazN4LU</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GEugARyP</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
+          <t>hEytAlL6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Wn71woN8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>IkSxE8Dt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EkqxE9x0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
+          <t>AqLzFcCb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dUjtW2Fr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>6kw90bc5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>MFnpCm7C</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>jyz8Ixzp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>UsklUtpe</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
+          <t>KW71BLSG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ddFjPf2b</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
+          <t>4zQgCGV0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sh9BS8ig</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
+          <t>plYXBAjf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dAfPwfHi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
+          <t>K8al4YeU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>pWQ6LC1N</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
+          <t>d6nbgHsC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>jiUEFsV1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
+          <t>E3bH2ZAd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>dY0SOQjI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>hQRLDaJc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hO8aNYWA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
+          <t>OSEc76Ak</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>vDA9yPiL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
+          <t>rFdeX5Xp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzeTFV7m</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
+          <t>GhQhDBYp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q9rcSKE7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
+          <t>6BbKeRcC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>zJCJQnM5</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+          <t>v3yHbxSH</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>QkntzCGG</t>
+          <t>pvekOSfU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>rRQ6H30k</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
+          <t>C4BrrfEE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YqcO2yDl</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+          <t>IVsJZ1cE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Ot6u6fRH</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ANq02KSh</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Gb1A9acT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>C43kVFJk</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>jXaKcHG7</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>KhqxObCM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>K6OAxbRF</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vcIeQx33</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>4Cs7LK8E</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>W61W8sP8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>bJWjBFBN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>j9HX6LgL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>M5JxAHIM</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>C64gDsb4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>xEisQlQH</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>4Wk6ieCO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>WprGGG4d</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>tzIzWVsQ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>vwhQPEQG</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>vuaksbnB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>0YJgAQC5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>pbJdKjM7</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>SQfscarm</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>jqtRXuSQ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>jT7X7Gd5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>dIO7tAAb</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>WKO7Omz0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>tj094etp</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>tr0QWSff</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>I9OrDysB</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>jDiLRtDc</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>6Xq5xjLq</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ALlse9Pi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>CpJVj93N</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Mi831aHr</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>SnzzjdRj</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>8G41omRp</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>jHHGvluB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>OvV1vKd3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>f1EO9xSh</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>IBytSAe5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>bweTPKsA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>lUWRGJsn</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>GIPMhVYA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>ATMcSJkl</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>OUFOxS9N</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>roLym02k</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>pbwYTWQh</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Wzwjgmf4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>GW4e7Um4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>EuGUBwlA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>8pGGBbct</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>2yu5QcK0</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>ltVl8SkJ</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>OrVmMCie</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>b5iIdGdU</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>Ac09TdRi</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Ey2Sg5SO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>ETqpict9</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>GUs6MFBb</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>dAMoEx1l</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>xng458IG</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>0fDYRkv8</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>CUnt4wLj</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>fkIM5gZp</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>r7dCawne</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>xQuFJbwR</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>46QpCnrg</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>OjTDOykD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>OOnl9jJi</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>YoI184sI</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>EwFQTB9e</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>zgw9F7bE</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>hzDGMR4C</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>0vgkewDa</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>KMvNIXAN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>pG6HYlQs</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>lhLarWun</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>OfoEKgtB</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>bZvl4Jlo</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>lWqPVhdt</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>OfLaQ95m</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>fFgcOysn</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>QkE2Af0D</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>2cth4tbt</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>Ma8YsCcM</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>bL1cTgl2</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>IN3HRzd4</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>OYqPDWLs</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>fJggJhbK</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>82DqAJKE</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>4U6h8ckR</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>faoX0Fs1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>2PluagCD</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>IXWRMd4K</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>E3IcHzSs</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>YuaKqZvA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>KtXllxbe</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>xE5BoeAc</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3.90</t>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>G8QcnGS7</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,32 +514,9966 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SWRIzxdS</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>AeRSxQrK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>fmqtFMjD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8WpYGrM0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>nHdPI4il</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>hdlcFVpd</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>jXP8f29S</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>htCzjMHq</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>z51uktXk</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>nu5ql0nd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>0rgRCqPd</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>vZiVB3v3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>dAnzBNg9</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>z1ovAs9F</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Sd97hFwr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>t0DBiZhl</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>C43exrWn</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ro9WXSv1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>I163zM0a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>GziuczET</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ERUq06ui</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>nuTibpA3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>2XnybGbN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>YFw7hfMp</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>hITmaQfc</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>0rXec4P9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>r7M0dOvG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>McL4erfM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>C6xBiEyi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>jT5F2vph</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>YieK1bab</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>xWC2qHqU</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>hrmC3KUo</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>tIbSaxUA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>KfIcpcUN</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>vuaUvyho</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>K8cWbdqH</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>t4JgowFH</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>CrfO0IE4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>lUEplQC8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>CORxkLFh</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>ETaCYaVB</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>jFQtluVb</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>hKbGXJpI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>nsbKWw0O</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>0p2OVcFU</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>Q7TUjsot</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>4bSYk10n</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>nsKknJaB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>YwGomap5</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>44mim5qC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>A1jaoqEO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>C6UsASjP</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>MuKH3QTh</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>I7DQ14b5</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>QDlmloU5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>hGjNfjnE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Us5SY8Pf</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Q9byXnf7</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>40cuW69D</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>dh57ZuG5</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>UuEjwOGt</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Ov7ay2og</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>KYplrD28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>A33cLkee</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>YykhsXHE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>zL5OZlAl</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>WC4gMVuk</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>vw81K9A1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>IT65JTP7</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>SbldtiXK</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>dU6KzVfr</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>6km0uBnR</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>EeOMRiIR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>KYOISX2L</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>trQETDmF</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>zokF8CBk</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>dfjB9hdq</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>WCrO6jt2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>pGW5VZI2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>O6V9UgY8</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>llFlNBQr</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>I9vK7WQe</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>jgBWGz49</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>nL4uFEYL</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>QB3qEYmS</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>8AVXeZRq</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>2XUyegsj</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>dWBSHGl3</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>n7P60FJS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>tOTufDdd</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>4dFzGfJF</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>IuDOIdZd</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>z3ro5w5c</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>Mavs6Jki</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>U5ierGcp</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>jLBYarTH</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>CUCU0ODB</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>8djaszDj</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>dIWg3HZ9</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>Qiyb2ykG</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>4rz21e4M</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>IRXk4cK3</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>449M2pqa</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>EFG95nat</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>bRnenPbI</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>rkLD46En</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>zkobxEe6</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>xlGack7J</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>MLiWiTUt</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>OWCIY5UI</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>Uoevj7ag</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>ptEEZoFC</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>2HO9zSa6</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>lEK5y8p0</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>GvF3d9MP</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>8xfrkREa</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>zPezimpm</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>G0McwUFm</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>2gtNqWxK</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>vL8Uwtk1</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>jJxJpCND</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>0U9QvMZf</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>8fDYx047</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>noCxxKJD</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>dGuRrjhQ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>bPRhvA0s</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>fiL1xlVg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>vVFzzC2U</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>Khe3WoFL</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>h0rLgzUq</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>nqgAsXvK</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>KGwjNsx8</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>QXEgHUR7</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>n3urP37e</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>fk6OJTnD</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>0SUSUgeE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>KzpTUYwH</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>8foZ2v7c</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>nk09A4h2</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>bw7fY7p9</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>Sb8nuyFj</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>jN60CQNk</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>jynZQPxq</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>dUdkad6M</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>QDOgGZON</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>hQ97NBml</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>0jDFLkI0</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>UoVpIefB</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>dGHGpciT</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>UNGpRiG6</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>8hYzTXPQ</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>jgmMIs3C</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>O8jKWf94</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>ddFPADno</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>xhhCYGvh</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>SWRIzxdS</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>hEytAlL6</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>IkSxE8Dt</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>AqLzFcCb</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>6kw90bc5</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>jyz8Ixzp</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>KW71BLSG</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>4zQgCGV0</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>plYXBAjf</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>K8al4YeU</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>d6nbgHsC</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>E3bH2ZAd</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>hQRLDaJc</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>OSEc76Ak</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>rFdeX5Xp</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>GhQhDBYp</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>6BbKeRcC</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>v3yHbxSH</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>pvekOSfU</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>C4BrrfEE</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>IVsJZ1cE</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>Ot6u6fRH</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>ANq02KSh</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>Gb1A9acT</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>C43kVFJk</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>jXaKcHG7</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>KhqxObCM</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>K6OAxbRF</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>vcIeQx33</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>4Cs7LK8E</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>W61W8sP8</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>bJWjBFBN</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>j9HX6LgL</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>M5JxAHIM</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>C64gDsb4</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>xEisQlQH</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>4Wk6ieCO</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>WprGGG4d</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>tzIzWVsQ</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>vwhQPEQG</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>vuaksbnB</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>0YJgAQC5</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>pbJdKjM7</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>SQfscarm</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>jqtRXuSQ</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>jT7X7Gd5</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>dIO7tAAb</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>WKO7Omz0</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>tj094etp</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>tr0QWSff</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>I9OrDysB</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>jDiLRtDc</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>6Xq5xjLq</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>ALlse9Pi</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>CpJVj93N</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>Mi831aHr</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>SnzzjdRj</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>8G41omRp</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>jHHGvluB</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>OvV1vKd3</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>f1EO9xSh</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>IBytSAe5</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>bweTPKsA</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>lUWRGJsn</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>GIPMhVYA</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>ATMcSJkl</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>OUFOxS9N</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>roLym02k</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>pbwYTWQh</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>Wzwjgmf4</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>GW4e7Um4</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>EuGUBwlA</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>8pGGBbct</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2yu5QcK0</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>ltVl8SkJ</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>OrVmMCie</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>b5iIdGdU</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>Ac09TdRi</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>Ey2Sg5SO</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>ETqpict9</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>GUs6MFBb</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>dAMoEx1l</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>xng458IG</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>0fDYRkv8</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>CUnt4wLj</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>fkIM5gZp</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>r7dCawne</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>xQuFJbwR</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>46QpCnrg</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>OjTDOykD</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>OOnl9jJi</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>YoI184sI</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>EwFQTB9e</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>zgw9F7bE</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>hzDGMR4C</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>0vgkewDa</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>KMvNIXAN</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>pG6HYlQs</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>lhLarWun</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>OfoEKgtB</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>bZvl4Jlo</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>lWqPVhdt</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>OfLaQ95m</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>fFgcOysn</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>QkE2Af0D</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2cth4tbt</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>Ma8YsCcM</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>bL1cTgl2</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>IN3HRzd4</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>OYqPDWLs</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>fJggJhbK</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>b9LHre3B</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>xU5RBAXB</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>GK4VAUnI</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>pClG5zQ1</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>KU4yDIXR</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>Gza5n1kb</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>YyoC6GAe</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
           <t>KGmbFEdf</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C362" t="inlineStr">
         <is>
           <t>3.80</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D362" t="inlineStr">
         <is>
           <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>82DqAJKE</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>4U6h8ckR</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>faoX0Fs1</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2PluagCD</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>IXWRMd4K</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>E3IcHzSs</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>YuaKqZvA</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>KtXllxbe</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>xE5BoeAc</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>G8QcnGS7</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>pKIPNiIj</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>8UHsapgU</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2meCcXHP</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>bJtrhBum</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>CrrhJmvn</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>ILdqjkAa</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>Qo0ilTvC</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>n1l0n79O</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>xQT96Aft</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>04EZ06OH</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>pCQRkLbJ</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>YJBMWNJa</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>INcgaD7l</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>pzkAeV6D</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>bwHM4ZqR</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>OK01cix1</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>4WLAk4Z3</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>IZPElOlA</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>0bFJmr4G</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>vkENn2JM</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>8OIRoMYS</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>AX4gstsp</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>hdfbt0dj</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>6FvA8wct</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>jsD1uKBd</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>4p1q43lc</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>zkqE7cCn</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>ry0m3N33</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>dpLdP7Lb</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>zeWeY24T</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>vTxmzPZG</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>hCzywRkb</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>W2Zvxo54</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>21EalzCO</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>0xvqy5KA</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>MiSiZrkN</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>46hrDJlP</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>WQHRStSj</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>WIN2iQ4i</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>A9M6jpKc</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>hzJNTMCp</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>ChwTrK5K</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>4jI7yxbf</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>hCE5NojB</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>IgMhQm6h</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>QPCDLPKN</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>fyBijdsC</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>lbAekGdI</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>nZD9M55H</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>r17IKqzU</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>pAgpG3ro</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>bDsSvmLo</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>AmoWw7zh</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>v9A1ORz5</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>COF1M5hj</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>YkKnUd7Q</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>8rBEPGFs</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>25AIOzVm</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>td9MNfpf</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>lOuihICa</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>Wp2ZKhUC</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>pl6wKCqJ</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>pS8oS9yt</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>GpCmixS5</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>OI7kRTjn</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>bX3RMEa0</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>xO2VLYE6</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>AXtmgbcg</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>jRUsVxhK</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>GAsqfvrm</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>pUwh8Fp7</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>OKxd7ZaD</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>CzWwWIxE</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>YTrCHJNK</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>CKsGGwwR</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>GlnyCcor</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>fuouBH0l</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>l2pqAyGf</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>25lm9eV0</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>f5UVqu2k</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>dQ0Ca0KP</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>jXNvrJW1</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>rRAQ5MO8</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>025V4tvF</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>27wueKSt</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>xra9cbWl</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>Ob1LfdG7</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>Q3u4Jug8</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>v7q8Ia8E</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>YF3w3K8R</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>GYcDdIoe</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>zcgGkAYA</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>SWk8iW3b</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>6H1aghZo</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>UJ8QycSI</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>SUAlX1Iq</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>0r9dVumd</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>x0hufPPd</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>ADjmh3f9</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>OGfiiN9F</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>IZ180t5J</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>pWr0k1vS</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>ILrLlUmH</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>hEcefYJu</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>l2WgmZd6</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>84KHwJc6</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>YkY5pXtP</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>YZeQtFkt</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>OOlwvDZb</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>xShswXl5</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>AuikyBJH</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>jT9MxwDC</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>x2NozVYN</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>290UuZ4n</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>ShVcngCC</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>8OObwbTs</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>C2tsLGDD</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>6FxXsvLQ</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>CGLFZFS6</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>fuBKYZsD</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>0xb6dwzK</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>vTdAeckQ</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>bDwsjyDm</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>WQyklFs0</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>dUGDvar0</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>4.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4009,6 +4009,8848 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>zwcBwqTP</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>r5DHBTv9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Kp7e4oXr</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>MZUbUvjC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>SzxjW0La</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>AyusUVeT</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>8UZIZZRi</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>xARZViRG</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>fqXMknIk</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>GbLVmQn2</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>4YtaO6OE</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>8W4PFuyJ</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Oru43jUb</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>WthfvVyR</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>KAYsYMjm</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Ox4C03W7</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>2XhHz2yn</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>0ARSCwSs</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>GbRWUxlQ</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>WCpYWJzB</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>OhdEZ36b</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>I9KbIKLH</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>lrh6iw43</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>bcLO4xyD</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>K4VeyRD5</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>YwdQcmuR</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>I5AeSkdt</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>vXfNMRbC</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>jaUqrSMj</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>MHsUEQcS</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>KCsUAHdf</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>WW4IdRyp</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>pIFVy6I7</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>IsdlPSY1</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>WlblghVi</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>WWGbDMV6</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>MLqiJCJP</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>KhoDI8b3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Sxox9eR6</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>fTrEmlaT</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>0MBBVesp</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>6kJ094Lk</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>WnwqL71s</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>lUSsM2Mh</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>0Uk5kAUG</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>zalWK5TO</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>YRgnVhvd</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>SAhNinbn</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>zRfR2QoD</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>UN4eVor9</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>pdMjKti5</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>dWHRJCuP</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2DUZNOit</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>KQM2PGBm</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>SvvsVc5N</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>0QcIa9AE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>SbbRf56d</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>pWf4j5X0</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>6RtwA8tC</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>EXFv49qA</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>b1HNwSme</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>Or3uRl4k</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>hOxchR2l</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>6mIDMoQH</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>l6EJLYAC</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>zm4m2mEM</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>EFM87rj2</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2issnpX7</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>z5NkFr1f</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>OnsQYu6b</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>EyE7GbjU</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Y7eVkQSb</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>b1wVBUBa</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>67CW5VEc</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>h4nciWa4</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>OAPCPyTp</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>Iqy8qcKG</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>GWO4Z4rI</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2gzn8nBO</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>MN2wyBFN</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>WIaMXsyB</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>4r62Vlwo</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>xAePbNGD</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>63xqoAeL</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>hvLANft0</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>0E33lZ3q</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>GKvMGnTF</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>lhZp7ZeJ</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>AyqzmWQ8</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>l4qimuLi</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>6oqDlq2D</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>xnTEulJr</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>dUnaoJk4</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>4AGA85Er</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>xnkMDjsm</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>x8QdQTQh</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>vVFzzC2U</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>Khe3WoFL</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>h0rLgzUq</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>nqgAsXvK</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>KGwjNsx8</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>QXEgHUR7</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>n3urP37e</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>fk6OJTnD</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>0SUSUgeE</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>KzpTUYwH</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>8foZ2v7c</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>nk09A4h2</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>bw7fY7p9</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>Sb8nuyFj</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>jN60CQNk</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>jynZQPxq</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>dUdkad6M</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>QDOgGZON</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>hQ97NBml</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>0jDFLkI0</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>UoVpIefB</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>dGHGpciT</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>UNGpRiG6</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>8hYzTXPQ</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>jgmMIs3C</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>O8jKWf94</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>ddFPADno</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>xhhCYGvh</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>SWRIzxdS</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>hEytAlL6</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>IkSxE8Dt</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>AqLzFcCb</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>6kw90bc5</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>jyz8Ixzp</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>KW71BLSG</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>4zQgCGV0</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>plYXBAjf</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>K8al4YeU</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>d6nbgHsC</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>E3bH2ZAd</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>hQRLDaJc</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>OSEc76Ak</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>rFdeX5Xp</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>GhQhDBYp</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>6BbKeRcC</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>v3yHbxSH</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>pvekOSfU</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>C4BrrfEE</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>IVsJZ1cE</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>Ot6u6fRH</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>ANq02KSh</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>Gb1A9acT</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>C43kVFJk</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>jXaKcHG7</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>KhqxObCM</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>K6OAxbRF</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>vcIeQx33</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>4Cs7LK8E</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>W61W8sP8</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>bJWjBFBN</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>j9HX6LgL</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>M5JxAHIM</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>C64gDsb4</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>xEisQlQH</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>4Wk6ieCO</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>WprGGG4d</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>tzIzWVsQ</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>vwhQPEQG</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>vuaksbnB</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>0YJgAQC5</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>pbJdKjM7</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>SQfscarm</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>jqtRXuSQ</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>jT7X7Gd5</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>dIO7tAAb</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>WKO7Omz0</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>tj094etp</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>tr0QWSff</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>I9OrDysB</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>jDiLRtDc</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>6Xq5xjLq</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>ALlse9Pi</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>CpJVj93N</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>Mi831aHr</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>SnzzjdRj</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>8G41omRp</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>jHHGvluB</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>OvV1vKd3</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>f1EO9xSh</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>IBytSAe5</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>bweTPKsA</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>lUWRGJsn</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>GIPMhVYA</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>ATMcSJkl</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>OUFOxS9N</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>roLym02k</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>pbwYTWQh</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>Wzwjgmf4</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>GW4e7Um4</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>EuGUBwlA</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>8pGGBbct</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2yu5QcK0</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>ltVl8SkJ</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>OrVmMCie</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>b5iIdGdU</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>Ac09TdRi</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>Ey2Sg5SO</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>ETqpict9</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>GUs6MFBb</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>dAMoEx1l</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>xng458IG</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>0fDYRkv8</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>CUnt4wLj</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>fkIM5gZp</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>r7dCawne</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>xQuFJbwR</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>46QpCnrg</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>OjTDOykD</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>OOnl9jJi</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>YoI184sI</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>EwFQTB9e</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>zgw9F7bE</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>hzDGMR4C</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>0vgkewDa</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>KMvNIXAN</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>pG6HYlQs</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>lhLarWun</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>OfoEKgtB</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>bZvl4Jlo</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>lWqPVhdt</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>OfLaQ95m</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>fFgcOysn</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>QkE2Af0D</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2cth4tbt</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>Ma8YsCcM</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>bL1cTgl2</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>IN3HRzd4</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>OYqPDWLs</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>fJggJhbK</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>b9LHre3B</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>xU5RBAXB</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>GK4VAUnI</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>pClG5zQ1</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>KU4yDIXR</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>Gza5n1kb</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>YyoC6GAe</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>A3eEI0Pp</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>4MvHxMGG</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>xAgY1xpS</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>dKJeVw9j</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>QyTPz0oT</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>CS1rgs1c</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>4deQ3bFF</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>pt0jiLV9</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>dfz5dG7k</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>G6L4SLit</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>Sti6DhR6</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>t62SsD9M</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>YJDXTDBm</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>AP8dO9uP</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2NJCQaMh</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>QwvaxiXq</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>bkDLOwi5</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>G2X0ZZmQ</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>6XBuSit0</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2a5lQVAC</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>lduFBWeJ</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>KGmbFEdf</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>82DqAJKE</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>4U6h8ckR</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>faoX0Fs1</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2PluagCD</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>IXWRMd4K</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>E3IcHzSs</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>YuaKqZvA</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>KtXllxbe</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>xE5BoeAc</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>G8QcnGS7</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>pKIPNiIj</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>8UHsapgU</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2meCcXHP</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>bJtrhBum</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>CrrhJmvn</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>ILdqjkAa</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>Qo0ilTvC</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>n1l0n79O</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>xQT96Aft</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>04EZ06OH</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>pCQRkLbJ</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>YJBMWNJa</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>INcgaD7l</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>pzkAeV6D</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>bwHM4ZqR</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>OK01cix1</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>4WLAk4Z3</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>IZPElOlA</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>0bFJmr4G</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>vkENn2JM</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>8OIRoMYS</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>AX4gstsp</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>hdfbt0dj</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>6FvA8wct</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>jsD1uKBd</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>4p1q43lc</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>zkqE7cCn</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>ry0m3N33</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>dpLdP7Lb</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>zeWeY24T</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>vTxmzPZG</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>hCzywRkb</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>W2Zvxo54</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>21EalzCO</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>0xvqy5KA</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>MiSiZrkN</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>46hrDJlP</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>WQHRStSj</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>WIN2iQ4i</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>A9M6jpKc</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>hzJNTMCp</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>ChwTrK5K</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>4jI7yxbf</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>hCE5NojB</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>IgMhQm6h</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>QPCDLPKN</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>fyBijdsC</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>lbAekGdI</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>nZD9M55H</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>r17IKqzU</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>pAgpG3ro</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>bDsSvmLo</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>AmoWw7zh</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>v9A1ORz5</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>COF1M5hj</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>YkKnUd7Q</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>8rBEPGFs</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>25AIOzVm</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>td9MNfpf</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>lOuihICa</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>Wp2ZKhUC</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>pl6wKCqJ</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>pS8oS9yt</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>GpCmixS5</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>OI7kRTjn</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>bX3RMEa0</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>xO2VLYE6</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>AXtmgbcg</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>jRUsVxhK</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>GAsqfvrm</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>pUwh8Fp7</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>OKxd7ZaD</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>CzWwWIxE</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>YTrCHJNK</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>CKsGGwwR</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>GlnyCcor</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>fuouBH0l</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>l2pqAyGf</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>25lm9eV0</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>f5UVqu2k</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>dQ0Ca0KP</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>jXNvrJW1</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>rRAQ5MO8</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>025V4tvF</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>27wueKSt</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>xra9cbWl</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>Ob1LfdG7</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>Q3u4Jug8</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>v7q8Ia8E</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>YF3w3K8R</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>GYcDdIoe</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>zcgGkAYA</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>SWk8iW3b</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>6H1aghZo</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>UJ8QycSI</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>SUAlX1Iq</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>0r9dVumd</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>x0hufPPd</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>ADjmh3f9</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>OGfiiN9F</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>IZ180t5J</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>pWr0k1vS</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>ILrLlUmH</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>hEcefYJu</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>l2WgmZd6</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>84KHwJc6</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>YkY5pXtP</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>YZeQtFkt</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>OOlwvDZb</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>xShswXl5</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>AuikyBJH</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>jT9MxwDC</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>x2NozVYN</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>290UuZ4n</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>ShVcngCC</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>8OObwbTs</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>C2tsLGDD</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>6FxXsvLQ</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>CGLFZFS6</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>fuBKYZsD</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>0xb6dwzK</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>vTdAeckQ</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>bDwsjyDm</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>WQyklFs0</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>dUGDvar0</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,484 +448,132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UwFBuMaf</t>
+          <t>4KwDffx2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhtVSrGl</t>
+          <t>bPy9vrn4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>21.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OIqwRMp1</t>
+          <t>riAVsHhd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d8abY4hR</t>
+          <t>Ac2H5Kp3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>41.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pYXoP0FD</t>
+          <t>2cr0t4Hi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xtzXn47K</t>
+          <t>jgVjka0M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>dQG3srVs</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Q58Kw0U6</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>W2BSyvaJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>C0axT3Xo</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>6XR3OUdM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>W2BTMHLH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Q3T1495j</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Cfx7zV1d</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>S2KgbYg3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>xhzmSCcc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>bV6rHnkd</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>6g3vy8tS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>b7OeQjS9</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QH8zJ8Kq</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pvFVxUBF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>xEBNvjs3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>3.40</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,132 +448,1232 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4KwDffx2</t>
+          <t>K0JghK0c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1.33</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bPy9vrn4</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>13.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>riAVsHhd</t>
+          <t>l6f1Na1N</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ac2H5Kp3</t>
+          <t>WQcQHwPp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2cr0t4Hi</t>
+          <t>bXkCusHi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jgVjka0M</t>
+          <t>4hy7UG8j</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Ei9MyY2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>rTas7Uuh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UPZ7hVQb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zPRNPuie</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MkDBaAbf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SlBjZEH8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EcoWEpWg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>z1qyZqU8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>b3dRq1rR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SKHfqRmo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>GMD4OFmp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Gpl1M6p3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>MkTOG61s</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>zeO4BBP1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>fZscvu6l</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>EJM6RNFa</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xIamkdK6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>8veHKF2F</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>dvGWNJL7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rVUmmzkJ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>rwwmB2VI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rD7AIOqS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.42</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>zm42KpFF</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>8x8WhvLs</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>zBnkBtx2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>lzCCMgId</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>441uiIkf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>2y3IoNDE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>SpqsD27k</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>dbvEzc5D</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>8Aoafidn</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>j1y6xJz1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>xfH0b0cK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>vTUeDXfk</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>UgqQIgXR</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>xjwGj9eB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SbOFR1Mr</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>8EsqXNbL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>0GI1dCOF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>OUZ4iTQ8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>KdTDk7eL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>juKqpoJr</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Cf8hrPme</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>0U3n46AE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>hSrRdO2l</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>xxfAVo4k</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>WzmJTPY1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Ys2f2puR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>pMLat3I7</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.91</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,555 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EJfDwuEj</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>p44sq1jT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8EJl8jJs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dtgtsEKr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2uy8aMzA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>fFXa1r6c</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hSxF3TVr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0QDzm8zG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6Pu8UaKl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>jD19YTxK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nqmuT70s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>rBtlRoVg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CUhG170e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>fDrzkU53</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SvUGSwk1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>z5XOQHJD</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2JelRQDd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>KMCY9qSa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Aau4hOTh</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bLBozsEO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jypdPPa6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2Zydfpat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RYCj2b5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Ao0VwPEa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KfdOaoV7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CjY4N3UI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ImLjo7MP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xY1Nuopm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0jZANlNE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6Dgvx3qC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,313 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>odds_home</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds_draw</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>odds_away</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>KMCY9qSa</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Aau4hOTh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>bLBozsEO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>jypdPPa6</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>2Zydfpat</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>6RYCj2b5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Ao0VwPEa</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>KfdOaoV7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>CjY4N3UI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ImLjo7MP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>xY1Nuopm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0jZANlNE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6Dgvx3qC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>vwSGH1jf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>